--- a/doctool/test/auto/scenario30/レビュー記録サマリ_S30_expected.xlsx
+++ b/doctool/test/auto/scenario30/レビュー記録サマリ_S30_expected.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1AD5DA-DCAE-4296-8EB9-C87481F5DABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32616D35-235E-4BBD-935C-D8E211E60589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9645" yWindow="4665" windowWidth="38700" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="4320" windowWidth="38700" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="品質指標" sheetId="4" r:id="rId1"/>
@@ -683,9 +683,6 @@
     <t>D00001</t>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S29</t>
-  </si>
-  <si>
     <t>鈴木　花子</t>
   </si>
   <si>
@@ -693,6 +690,10 @@
   </si>
   <si>
     <t>回覧</t>
+  </si>
+  <si>
+    <t>システム機能設計書_サンプル_S30</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1927,10 +1928,10 @@
       </c>
       <c r="E6" s="43"/>
       <c r="F6" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="44" t="s">
         <v>91</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>92</v>
       </c>
       <c r="H6" s="45">
         <v>1</v>
@@ -1958,7 +1959,7 @@
         <v>200</v>
       </c>
       <c r="Q6" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R6" s="53"/>
       <c r="S6" s="53"/>
@@ -1966,11 +1967,11 @@
       <c r="U6" s="53"/>
       <c r="V6" s="53"/>
       <c r="W6" s="54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="X6" s="53"/>
       <c r="Y6" s="55" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z6" s="56">
         <f t="shared" ref="Z6" si="1">IF(Y6="回覧",COUNTA(Q6:V6),COUNTA(Q6:X6))</f>
@@ -2017,12 +2018,12 @@
   </sheetData>
   <autoFilter ref="A5:AR5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="6">
+    <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AH4:AH5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A6:AN6">
